--- a/cypress/downloads/resultsApproval_Assignmaintenace.xlsx
+++ b/cypress/downloads/resultsApproval_Assignmaintenace.xlsx
@@ -397,10 +397,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:C7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Button Clicked</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-02-27T07:15:16.392Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>User masuk ke Page PV Master List Maintenance</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-02-27T07:15:16.393Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>user check button assign Vendor in tbigsys</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-02-27T07:15:16.396Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>User ID Input</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-02-27T07:15:16.890Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Password has been inputed</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-02-27T07:15:17.162Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Site ID has been found</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2026-02-27T07:15:26.406Z</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>